--- a/SAP Reports/Input Files/Bal-Sht Feb 26/BS CHALLMC FEB 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/Bal-Sht Feb 26/BS CHALLMC FEB 26 ANNUAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="208">
   <si>
     <t>Account Name</t>
   </si>
@@ -34,486 +34,474 @@
     <t>Assets</t>
   </si>
   <si>
-    <t>$  4,239,560.90</t>
-  </si>
-  <si>
-    <t>$  5,069,091.89</t>
-  </si>
-  <si>
-    <t>$ -829,530.99</t>
-  </si>
-  <si>
-    <t>% -16.364</t>
+    <t>$  6,144,147.75</t>
+  </si>
+  <si>
+    <t>$  5,058,591.54</t>
+  </si>
+  <si>
+    <t>$ 1,085,556.21</t>
+  </si>
+  <si>
+    <t>% 21.460</t>
   </si>
   <si>
     <t>Current Assets - Cash and Equiv</t>
   </si>
   <si>
-    <t>$  4,096,707.16</t>
-  </si>
-  <si>
-    <t>$  4,940,527.94</t>
-  </si>
-  <si>
-    <t>$ -843,820.78</t>
-  </si>
-  <si>
-    <t>% -17.080</t>
+    <t>$  6,001,294.01</t>
+  </si>
+  <si>
+    <t>$  4,930,027.59</t>
+  </si>
+  <si>
+    <t>$ 1,071,266.42</t>
+  </si>
+  <si>
+    <t>% 21.729</t>
   </si>
   <si>
     <t>Cash and Equiv - CASH AND EQUITY</t>
   </si>
   <si>
-    <t>$  2,677,659.80</t>
+    <t>$  4,374,595.12</t>
   </si>
   <si>
     <t>$  2,146,549.01</t>
   </si>
   <si>
-    <t>$ 531,110.79</t>
-  </si>
-  <si>
-    <t>% 24.743</t>
+    <t>$ 2,228,046.11</t>
+  </si>
+  <si>
+    <t>% 103.797</t>
   </si>
   <si>
     <t>110101-02-000-00 - SSB-CHECKING ACCT</t>
   </si>
   <si>
-    <t>$  658,704.52</t>
+    <t>$  783,024.30</t>
   </si>
   <si>
     <t>$  1,439,593.84</t>
   </si>
   <si>
-    <t>$ -780,889.32</t>
-  </si>
-  <si>
-    <t>% -54.244</t>
+    <t>$ -656,569.54</t>
+  </si>
+  <si>
+    <t>% -45.608</t>
   </si>
   <si>
     <t>110400-02-000-00 - SSB HIGH YIELD MMKT</t>
   </si>
   <si>
+    <t>$  756,955.17</t>
+  </si>
+  <si>
     <t>$  6,955.17</t>
   </si>
   <si>
+    <t>$ 750,000.00</t>
+  </si>
+  <si>
+    <t>% 10,783.345</t>
+  </si>
+  <si>
     <t>110450-02-000-00 - INTER DIVISION BANK</t>
   </si>
   <si>
-    <t>$  2,000,000.00</t>
+    <t>$  2,834,615.65</t>
   </si>
   <si>
     <t>$  700,000.00</t>
   </si>
   <si>
-    <t>$ 1,300,000.00</t>
-  </si>
-  <si>
-    <t>% 185.714</t>
-  </si>
-  <si>
-    <t>110705-02-000-00 - CHECKING CLEARING ACCOUNT</t>
-  </si>
-  <si>
-    <t>$  12,000.11</t>
-  </si>
-  <si>
-    <t>$ 12,000.11</t>
+    <t>$ 2,134,615.65</t>
+  </si>
+  <si>
+    <t>% 304.945</t>
+  </si>
+  <si>
+    <t>__________________</t>
+  </si>
+  <si>
+    <t>Total Cash and Equiv - CASH AND EQUITY</t>
+  </si>
+  <si>
+    <t>- - - - - - - - - - - - -</t>
+  </si>
+  <si>
+    <t>Receivables - RECEIVABLES</t>
+  </si>
+  <si>
+    <t>$  1,621,098.89</t>
+  </si>
+  <si>
+    <t>$  2,777,878.58</t>
+  </si>
+  <si>
+    <t>$ -1,156,779.69</t>
+  </si>
+  <si>
+    <t>% -41.643</t>
+  </si>
+  <si>
+    <t>120000-02-000-00 - ACCOUNTS RECEIVABLE</t>
+  </si>
+  <si>
+    <t>$  3,551,831.35</t>
+  </si>
+  <si>
+    <t>$  3,809,611.04</t>
+  </si>
+  <si>
+    <t>$ -257,779.69</t>
+  </si>
+  <si>
+    <t>% -6.767</t>
+  </si>
+  <si>
+    <t>120015-02-000-00 - LOAN TO/FROM TGI</t>
+  </si>
+  <si>
+    <t>$  150,000.00</t>
+  </si>
+  <si>
+    <t>120045-02-000-00 - LOAN TO/FROM BMLLC</t>
+  </si>
+  <si>
+    <t>$ (2,100,000.00)</t>
+  </si>
+  <si>
+    <t>$ (1,200,000.00)</t>
+  </si>
+  <si>
+    <t>$ -900,000.00</t>
+  </si>
+  <si>
+    <t>% -75.000</t>
+  </si>
+  <si>
+    <t>120060-02-000-00 - LOAN TO EMPLOYEE</t>
+  </si>
+  <si>
+    <t>$  19,267.54</t>
+  </si>
+  <si>
+    <t>$  18,267.54</t>
+  </si>
+  <si>
+    <t>$ 1,000.00</t>
+  </si>
+  <si>
+    <t>% 5.474</t>
+  </si>
+  <si>
+    <t>Total Receivables - RECEIVABLES</t>
+  </si>
+  <si>
+    <t>Other Current - OTHER CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t>$  5,600.00</t>
+  </si>
+  <si>
+    <t>120452-02-000-00 - SECURITY DEPOSIT (PEPCO &amp; GAS)</t>
+  </si>
+  <si>
+    <t>Total Other Current - OTHER CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t>Total Current Assets - Cash and Equiv</t>
+  </si>
+  <si>
+    <t>Fixed Assets - FIXED ASSETS</t>
+  </si>
+  <si>
+    <t>$  20,002.74</t>
+  </si>
+  <si>
+    <t>$  5,712.95</t>
+  </si>
+  <si>
+    <t>$ 14,289.79</t>
+  </si>
+  <si>
+    <t>% 250.130</t>
+  </si>
+  <si>
+    <t>FixedAssets - FIXED ASSETS</t>
+  </si>
+  <si>
+    <t>$  1,735,786.09</t>
+  </si>
+  <si>
+    <t>$  1,721,496.30</t>
+  </si>
+  <si>
+    <t>% 0.830</t>
+  </si>
+  <si>
+    <t>120470-02-000-00 - COMPUTER/OFFICE MACHINES</t>
+  </si>
+  <si>
+    <t>$  98,329.48</t>
+  </si>
+  <si>
+    <t>120500-02-000-00 - SHOP MACHINERY &amp; EQUIPMENT</t>
+  </si>
+  <si>
+    <t>$  237,643.63</t>
+  </si>
+  <si>
+    <t>120550-02-000-00 - FURNITURE &amp; FIXTURES</t>
+  </si>
+  <si>
+    <t>$  18,497.35</t>
+  </si>
+  <si>
+    <t>120600-02-000-00 - LEASEHOLD IMPROVEMENT</t>
+  </si>
+  <si>
+    <t>$  691,993.64</t>
+  </si>
+  <si>
+    <t>$  686,703.85</t>
+  </si>
+  <si>
+    <t>$ 5,289.79</t>
+  </si>
+  <si>
+    <t>% 0.770</t>
+  </si>
+  <si>
+    <t>120650-02-000-00 - HVAC</t>
+  </si>
+  <si>
+    <t>$  208,256.56</t>
+  </si>
+  <si>
+    <t>$  199,256.56</t>
+  </si>
+  <si>
+    <t>$ 9,000.00</t>
+  </si>
+  <si>
+    <t>% 4.517</t>
+  </si>
+  <si>
+    <t>120700-02-000-00 - VEHICLES &amp; HEAV EQUIP</t>
+  </si>
+  <si>
+    <t>$  318,113.34</t>
+  </si>
+  <si>
+    <t>120750-02-000-00 - GAS STATION-ON SITE</t>
+  </si>
+  <si>
+    <t>$  99,300.00</t>
+  </si>
+  <si>
+    <t>120800-02-000-00 - PARTITIONS</t>
+  </si>
+  <si>
+    <t>$  63,652.09</t>
+  </si>
+  <si>
+    <t>Total FixedAssets - FIXED ASSETS</t>
+  </si>
+  <si>
+    <t>Accum Depn - ACCUMULATED DEPRECIATION</t>
+  </si>
+  <si>
+    <t>$ (1,715,783.35)</t>
+  </si>
+  <si>
+    <t>121470-02-000-00 - ACCUM COMPUTER/OFFICE MACH</t>
+  </si>
+  <si>
+    <t>$ (98,329.27)</t>
+  </si>
+  <si>
+    <t>121500-02-000-00 - ACCUM (SHOP MACHINERY &amp; EQUIPMENT)</t>
+  </si>
+  <si>
+    <t>$ (192,487.93)</t>
+  </si>
+  <si>
+    <t>121550-02-000-00 - ACCUM FURNITURE &amp; FIXTURES</t>
+  </si>
+  <si>
+    <t>$ (18,497.35)</t>
+  </si>
+  <si>
+    <t>121600-02-000-00 - ACCUM LEASEHOLD IMPROVEMENT</t>
+  </si>
+  <si>
+    <t>$ (686,706.90)</t>
+  </si>
+  <si>
+    <t>121700-02-000-00 - ACCUM VEHICLES &amp; HEAV EQUIP</t>
+  </si>
+  <si>
+    <t>$ (357,553.34)</t>
+  </si>
+  <si>
+    <t>121720-02-000-00 - ACCUM GAS STATION</t>
+  </si>
+  <si>
+    <t>$ (99,300.00)</t>
+  </si>
+  <si>
+    <t>121740-02-000-00 - ACUM DEP PARTITIONS</t>
+  </si>
+  <si>
+    <t>$ (63,652.09)</t>
+  </si>
+  <si>
+    <t>121650-02-000-00 - ACUM DEP HVAC</t>
+  </si>
+  <si>
+    <t>$ (199,256.47)</t>
+  </si>
+  <si>
+    <t>Total Accum Depn - ACCUMULATED DEPRECIATION</t>
+  </si>
+  <si>
+    <t>Total Fixed Assets - FIXED ASSETS</t>
+  </si>
+  <si>
+    <t>120621-02-000-00 - Prepaid MD PTET</t>
+  </si>
+  <si>
+    <t>$  122,851.00</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>=============</t>
+  </si>
+  <si>
+    <t>Liabilities</t>
+  </si>
+  <si>
+    <t>$  1,819,840.48</t>
+  </si>
+  <si>
+    <t>$  869,039.34</t>
+  </si>
+  <si>
+    <t>$ 950,801.14</t>
+  </si>
+  <si>
+    <t>% 109.408</t>
+  </si>
+  <si>
+    <t>Current Liabs - CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>$  319,840.48</t>
+  </si>
+  <si>
+    <t>$ -549,198.86</t>
+  </si>
+  <si>
+    <t>% -63.196</t>
+  </si>
+  <si>
+    <t>Accts Payable - ACCOUNTS PAYABLE</t>
+  </si>
+  <si>
+    <t>Total Accts Payable - ACCOUNTS PAYABLE</t>
+  </si>
+  <si>
+    <t>Payroll Liabs - PAYROLL LIABILITIES</t>
+  </si>
+  <si>
+    <t>$  315,279.70</t>
+  </si>
+  <si>
+    <t>$  864,656.20</t>
+  </si>
+  <si>
+    <t>$ -549,376.50</t>
+  </si>
+  <si>
+    <t>% -63.537</t>
+  </si>
+  <si>
+    <t>220256-02-000-00 - WAGES PAYABLES</t>
+  </si>
+  <si>
+    <t>$  312,423.13</t>
+  </si>
+  <si>
+    <t>$  863,283.00</t>
+  </si>
+  <si>
+    <t>$ -550,859.87</t>
+  </si>
+  <si>
+    <t>% -63.810</t>
+  </si>
+  <si>
+    <t>250900-02-000-00 - 401 K LIABILITY -PAYABLE</t>
+  </si>
+  <si>
+    <t>$  2,856.57</t>
+  </si>
+  <si>
+    <t>$  1,373.20</t>
+  </si>
+  <si>
+    <t>$ 1,483.37</t>
+  </si>
+  <si>
+    <t>% 108.023</t>
+  </si>
+  <si>
+    <t>Total Payroll Liabs - PAYROLL LIABILITIES</t>
+  </si>
+  <si>
+    <t>OtherLiability - OTHER LIBILITY</t>
+  </si>
+  <si>
+    <t>$  4,560.78</t>
+  </si>
+  <si>
+    <t>$  4,383.14</t>
+  </si>
+  <si>
+    <t>$ 177.64</t>
+  </si>
+  <si>
+    <t>% 4.053</t>
+  </si>
+  <si>
+    <t>220260-02-000-00 - AFLAC PAYABLES</t>
+  </si>
+  <si>
+    <t>$  4,307.76</t>
+  </si>
+  <si>
+    <t>$ -75.38</t>
+  </si>
+  <si>
+    <t>% -1.720</t>
+  </si>
+  <si>
+    <t>250920-02-000-00 - HUMANA INS(VISION &amp; DENTAL)</t>
+  </si>
+  <si>
+    <t>$  253.02</t>
+  </si>
+  <si>
+    <t>$ 253.02</t>
   </si>
   <si>
     <t>****</t>
   </si>
   <si>
-    <t>__________________</t>
-  </si>
-  <si>
-    <t>Total Cash and Equiv - CASH AND EQUITY</t>
-  </si>
-  <si>
-    <t>- - - - - - - - - - - - -</t>
-  </si>
-  <si>
-    <t>Receivables - RECEIVABLES</t>
-  </si>
-  <si>
-    <t>$  1,412,271.54</t>
-  </si>
-  <si>
-    <t>$  2,788,378.93</t>
-  </si>
-  <si>
-    <t>$ -1,376,107.39</t>
-  </si>
-  <si>
-    <t>% -49.352</t>
-  </si>
-  <si>
-    <t>120000-02-000-00 - ACCOUNTS RECEIVABLE</t>
-  </si>
-  <si>
-    <t>$  3,642,004.00</t>
-  </si>
-  <si>
-    <t>$  3,820,111.39</t>
-  </si>
-  <si>
-    <t>$ -178,107.39</t>
-  </si>
-  <si>
-    <t>% -4.662</t>
-  </si>
-  <si>
-    <t>120015-02-000-00 - LOAN TO/FROM TGI</t>
-  </si>
-  <si>
-    <t>$  150,000.00</t>
-  </si>
-  <si>
-    <t>120045-02-000-00 - LOAN TO/FROM BMLLC</t>
-  </si>
-  <si>
-    <t>$ (2,400,000.00)</t>
-  </si>
-  <si>
-    <t>$ (1,200,000.00)</t>
-  </si>
-  <si>
-    <t>$ -1,200,000.00</t>
-  </si>
-  <si>
-    <t>% -100.000</t>
-  </si>
-  <si>
-    <t>120060-02-000-00 - LOAN TO EMPLOYEE</t>
-  </si>
-  <si>
-    <t>$  20,267.54</t>
-  </si>
-  <si>
-    <t>$  18,267.54</t>
-  </si>
-  <si>
-    <t>$ 2,000.00</t>
-  </si>
-  <si>
-    <t>% 10.948</t>
-  </si>
-  <si>
-    <t>Total Receivables - RECEIVABLES</t>
-  </si>
-  <si>
-    <t>Other Current - OTHER CURRENT ASSETS</t>
-  </si>
-  <si>
-    <t>$  6,775.82</t>
-  </si>
-  <si>
-    <t>$  5,600.00</t>
-  </si>
-  <si>
-    <t>$ 1,175.82</t>
-  </si>
-  <si>
-    <t>% 20.997</t>
-  </si>
-  <si>
-    <t>120452-02-000-00 - SECURITY DEPOSIT (PEPCO &amp; GAS)</t>
-  </si>
-  <si>
-    <t>121810-02-000-00 - DUE TO PAYCHEX</t>
-  </si>
-  <si>
-    <t>$  1,175.82</t>
-  </si>
-  <si>
-    <t>Total Other Current - OTHER CURRENT ASSETS</t>
-  </si>
-  <si>
-    <t>Total Current Assets - Cash and Equiv</t>
-  </si>
-  <si>
-    <t>Fixed Assets - FIXED ASSETS</t>
-  </si>
-  <si>
-    <t>$  20,002.74</t>
-  </si>
-  <si>
-    <t>$  5,712.95</t>
-  </si>
-  <si>
-    <t>$ 14,289.79</t>
-  </si>
-  <si>
-    <t>% 250.130</t>
-  </si>
-  <si>
-    <t>FixedAssets - FIXED ASSETS</t>
-  </si>
-  <si>
-    <t>$  1,735,786.09</t>
-  </si>
-  <si>
-    <t>$  1,721,496.30</t>
-  </si>
-  <si>
-    <t>% 0.830</t>
-  </si>
-  <si>
-    <t>120470-02-000-00 - COMPUTER/OFFICE MACHINES</t>
-  </si>
-  <si>
-    <t>$  98,329.48</t>
-  </si>
-  <si>
-    <t>120500-02-000-00 - SHOP MACHINERY &amp; EQUIPMENT</t>
-  </si>
-  <si>
-    <t>$  237,643.63</t>
-  </si>
-  <si>
-    <t>120550-02-000-00 - FURNITURE &amp; FIXTURES</t>
-  </si>
-  <si>
-    <t>$  18,497.35</t>
-  </si>
-  <si>
-    <t>120600-02-000-00 - LEASEHOLD IMPROVEMENT</t>
-  </si>
-  <si>
-    <t>$  691,993.64</t>
-  </si>
-  <si>
-    <t>$  686,703.85</t>
-  </si>
-  <si>
-    <t>$ 5,289.79</t>
-  </si>
-  <si>
-    <t>% 0.770</t>
-  </si>
-  <si>
-    <t>120650-02-000-00 - HVAC</t>
-  </si>
-  <si>
-    <t>$  208,256.56</t>
-  </si>
-  <si>
-    <t>$  199,256.56</t>
-  </si>
-  <si>
-    <t>$ 9,000.00</t>
-  </si>
-  <si>
-    <t>% 4.517</t>
-  </si>
-  <si>
-    <t>120700-02-000-00 - VEHICLES &amp; HEAV EQUIP</t>
-  </si>
-  <si>
-    <t>$  318,113.34</t>
-  </si>
-  <si>
-    <t>120750-02-000-00 - GAS STATION-ON SITE</t>
-  </si>
-  <si>
-    <t>$  99,300.00</t>
-  </si>
-  <si>
-    <t>120800-02-000-00 - PARTITIONS</t>
-  </si>
-  <si>
-    <t>$  63,652.09</t>
-  </si>
-  <si>
-    <t>Total FixedAssets - FIXED ASSETS</t>
-  </si>
-  <si>
-    <t>Accum Depn - ACCUMULATED DEPRECIATION</t>
-  </si>
-  <si>
-    <t>$ (1,715,783.35)</t>
-  </si>
-  <si>
-    <t>121470-02-000-00 - ACCUM COMPUTER/OFFICE MACH</t>
-  </si>
-  <si>
-    <t>$ (98,329.27)</t>
-  </si>
-  <si>
-    <t>121500-02-000-00 - ACCUM (SHOP MACHINERY &amp; EQUIPMENT)</t>
-  </si>
-  <si>
-    <t>$ (192,487.93)</t>
-  </si>
-  <si>
-    <t>121550-02-000-00 - ACCUM FURNITURE &amp; FIXTURES</t>
-  </si>
-  <si>
-    <t>$ (18,497.35)</t>
-  </si>
-  <si>
-    <t>121600-02-000-00 - ACCUM LEASEHOLD IMPROVEMENT</t>
-  </si>
-  <si>
-    <t>$ (686,706.90)</t>
-  </si>
-  <si>
-    <t>121700-02-000-00 - ACCUM VEHICLES &amp; HEAV EQUIP</t>
-  </si>
-  <si>
-    <t>$ (357,553.34)</t>
-  </si>
-  <si>
-    <t>121720-02-000-00 - ACCUM GAS STATION</t>
-  </si>
-  <si>
-    <t>$ (99,300.00)</t>
-  </si>
-  <si>
-    <t>121740-02-000-00 - ACUM DEP PARTITIONS</t>
-  </si>
-  <si>
-    <t>$ (63,652.09)</t>
-  </si>
-  <si>
-    <t>121650-02-000-00 - ACUM DEP HVAC</t>
-  </si>
-  <si>
-    <t>$ (199,256.47)</t>
-  </si>
-  <si>
-    <t>Total Accum Depn - ACCUMULATED DEPRECIATION</t>
-  </si>
-  <si>
-    <t>Total Fixed Assets - FIXED ASSETS</t>
-  </si>
-  <si>
-    <t>120621-02-000-00 - Prepaid MD PTET</t>
-  </si>
-  <si>
-    <t>$  122,851.00</t>
-  </si>
-  <si>
-    <t>Total Assets</t>
-  </si>
-  <si>
-    <t>=============</t>
-  </si>
-  <si>
-    <t>Liabilities</t>
-  </si>
-  <si>
-    <t>$  301,687.55</t>
-  </si>
-  <si>
-    <t>$  869,039.34</t>
-  </si>
-  <si>
-    <t>$ -567,351.79</t>
-  </si>
-  <si>
-    <t>% -65.285</t>
-  </si>
-  <si>
-    <t>Current Liabs - CURRENT LIABILITIES</t>
-  </si>
-  <si>
-    <t>Accts Payable - ACCOUNTS PAYABLE</t>
-  </si>
-  <si>
-    <t>$  43,910.60</t>
-  </si>
-  <si>
-    <t>$ 43,910.60</t>
-  </si>
-  <si>
-    <t>220040-02-000-00 - ACCOUNTS PAYABLE</t>
-  </si>
-  <si>
-    <t>Total Accts Payable - ACCOUNTS PAYABLE</t>
-  </si>
-  <si>
-    <t>Payroll Liabs - PAYROLL LIABILITIES</t>
-  </si>
-  <si>
-    <t>$  260,643.00</t>
-  </si>
-  <si>
-    <t>$  864,656.20</t>
-  </si>
-  <si>
-    <t>$ -604,013.20</t>
-  </si>
-  <si>
-    <t>% -69.856</t>
-  </si>
-  <si>
-    <t>220256-02-000-00 - WAGES PAYABLES</t>
-  </si>
-  <si>
-    <t>$  247,600.32</t>
-  </si>
-  <si>
-    <t>$  863,283.00</t>
-  </si>
-  <si>
-    <t>$ -615,682.68</t>
-  </si>
-  <si>
-    <t>% -71.319</t>
-  </si>
-  <si>
-    <t>250900-02-000-00 - 401 K LIABILITY -PAYABLE</t>
-  </si>
-  <si>
-    <t>$  13,042.68</t>
-  </si>
-  <si>
-    <t>$  1,373.20</t>
-  </si>
-  <si>
-    <t>$ 11,669.48</t>
-  </si>
-  <si>
-    <t>% 849.802</t>
-  </si>
-  <si>
-    <t>Total Payroll Liabs - PAYROLL LIABILITIES</t>
-  </si>
-  <si>
-    <t>OtherLiability - OTHER LIBILITY</t>
-  </si>
-  <si>
-    <t>$ (2,866.05)</t>
-  </si>
-  <si>
-    <t>$  4,383.14</t>
-  </si>
-  <si>
-    <t>$ -7,249.19</t>
-  </si>
-  <si>
-    <t>220260-02-000-00 - AFLAC PAYABLES</t>
-  </si>
-  <si>
-    <t>$  114.60</t>
-  </si>
-  <si>
-    <t>$ -4,268.54</t>
-  </si>
-  <si>
-    <t>% -97.385</t>
-  </si>
-  <si>
-    <t>250920-02-000-00 - HUMANA INS(VISION &amp; DENTAL)</t>
-  </si>
-  <si>
-    <t>$ (2,980.65)</t>
-  </si>
-  <si>
-    <t>$ -2,980.65</t>
-  </si>
-  <si>
     <t>Total OtherLiability - OTHER LIBILITY</t>
   </si>
   <si>
@@ -523,9 +511,18 @@
     <t>L/Term Liabs - LONG TERM LIABILITIES</t>
   </si>
   <si>
+    <t>$  1,500,000.00</t>
+  </si>
+  <si>
+    <t>$ 1,500,000.00</t>
+  </si>
+  <si>
     <t>Other L/T Liabs - OTHER LONG TERM LIBILITIES</t>
   </si>
   <si>
+    <t>252000-02-000-00 - LOAN FROM MATTHEW MOHEBBI</t>
+  </si>
+  <si>
     <t>Total Other L/T Liabs - OTHER LONG TERM LIBILITIES</t>
   </si>
   <si>
@@ -538,31 +535,31 @@
     <t>Equity</t>
   </si>
   <si>
-    <t>$  3,937,873.35</t>
-  </si>
-  <si>
-    <t>$  4,200,052.55</t>
-  </si>
-  <si>
-    <t>$ -262,179.20</t>
-  </si>
-  <si>
-    <t>% -6.242</t>
+    <t>$  4,324,307.27</t>
+  </si>
+  <si>
+    <t>$  4,189,552.20</t>
+  </si>
+  <si>
+    <t>$ 134,755.07</t>
+  </si>
+  <si>
+    <t>% 3.216</t>
   </si>
   <si>
     <t>Stock Equity - STOCK HOLDERS EQUITY</t>
   </si>
   <si>
-    <t>$  3,761,458.56</t>
+    <t>$  3,676,458.56</t>
   </si>
   <si>
     <t>$  3,595,458.56</t>
   </si>
   <si>
-    <t>$ 166,000.00</t>
-  </si>
-  <si>
-    <t>% 4.617</t>
+    <t>$ 81,000.00</t>
+  </si>
+  <si>
+    <t>% 2.253</t>
   </si>
   <si>
     <t>Common Stock - COMMON STOCK</t>
@@ -592,13 +589,13 @@
     <t>Surplus - SURPLUS</t>
   </si>
   <si>
-    <t>$  3,342,245.56</t>
+    <t>$  3,257,245.56</t>
   </si>
   <si>
     <t>$  3,176,245.56</t>
   </si>
   <si>
-    <t>% 5.226</t>
+    <t>% 2.550</t>
   </si>
   <si>
     <t>368400-02-000-00 - RETAINED EARNINGS</t>
@@ -610,13 +607,13 @@
     <t>368350-02-000-00 - PROFIT DISTRIBUTION</t>
   </si>
   <si>
-    <t>$ (4,394,252.00)</t>
+    <t>$ (4,479,252.00)</t>
   </si>
   <si>
     <t>$ (4,560,252.00)</t>
   </si>
   <si>
-    <t>% 3.640</t>
+    <t>% 1.776</t>
   </si>
   <si>
     <t>Total Surplus - SURPLUS</t>
@@ -628,16 +625,16 @@
     <t>Profit Period</t>
   </si>
   <si>
-    <t>$  176,414.79</t>
-  </si>
-  <si>
-    <t>$  604,593.99</t>
-  </si>
-  <si>
-    <t>$ -428,179.20</t>
-  </si>
-  <si>
-    <t>% -70.821</t>
+    <t>$  647,848.71</t>
+  </si>
+  <si>
+    <t>$  594,093.64</t>
+  </si>
+  <si>
+    <t>$ 53,755.07</t>
+  </si>
+  <si>
+    <t>% 9.048</t>
   </si>
   <si>
     <t>Total Equity</t>
@@ -1587,666 +1584,654 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
       <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="s">
+		</row>
+    <row r="15">
+      <c r="A15" t="s">
         <v>38</v>
       </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15">
-		</row>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" t="s">
+		</row>
+    <row r="17">
+      <c r="A17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17">
-		</row>
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22">
       <c r="B22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="s">
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24">
+		</row>
+    <row r="25">
+      <c r="A25" t="s">
         <v>61</v>
       </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25">
-		</row>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" t="s">
+		</row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27">
-		</row>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" t="s">
-        <v>35</v>
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" t="s">
-        <v>66</v>
-      </c>
-    </row>
+		</row>
     <row r="32">
       <c r="B32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
-		</row>
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
-      </c>
-    </row>
+		</row>
     <row r="36">
+      <c r="A36" t="s">
+        <v>66</v>
+      </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>68</v>
+      </c>
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="37">
 		</row>
     <row r="38">
       <c r="A38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
         <v>72</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>73</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" t="s">
         <v>74</v>
-      </c>
-      <c r="D38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="39">
 		</row>
     <row r="40">
       <c r="A40" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
         <v>77</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>78</v>
       </c>
-      <c r="C40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D40" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41">
-		</row>
+      <c r="C41" t="s">
+        <v>78</v>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
         <v>83</v>
       </c>
-      <c r="B43" t="s">
+      <c r="D43" t="s">
         <v>84</v>
       </c>
-      <c r="C43" t="s">
-        <v>84</v>
+      <c r="E43" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C46" t="s">
         <v>94</v>
       </c>
-      <c r="D46" t="s">
-        <v>95</v>
-      </c>
-      <c r="E46" t="s">
-        <v>96</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>99</v>
-      </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>73</v>
+      </c>
+      <c r="D49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E49" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" t="s">
-        <v>80</v>
-      </c>
-    </row>
+		</row>
     <row r="52">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
 		</row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55">
-		</row>
+      <c r="A55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B55" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B61" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="s">
-        <v>118</v>
-      </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="s">
-        <v>122</v>
-      </c>
-      <c r="B65" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" t="s">
-        <v>105</v>
-      </c>
-    </row>
+		</row>
     <row r="66">
       <c r="B66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
-		</row>
+      <c r="A67" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" t="s">
+        <v>70</v>
+      </c>
+    </row>
     <row r="68">
       <c r="B68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
-        <v>123</v>
-      </c>
-      <c r="B69" t="s">
-        <v>73</v>
-      </c>
-      <c r="C69" t="s">
-        <v>74</v>
-      </c>
-      <c r="D69" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" t="s">
-        <v>76</v>
-      </c>
-    </row>
+		</row>
     <row r="70">
+      <c r="A70" t="s">
+        <v>118</v>
+      </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71">
-		</row>
+      <c r="B71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C71" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B72" t="s">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>125</v>
+        <v>7</v>
+      </c>
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C73" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
-        <v>126</v>
-      </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
@@ -2262,655 +2247,676 @@
     </row>
     <row r="75">
       <c r="B75" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" t="s">
-        <v>8</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-    </row>
+		</row>
     <row r="77">
+      <c r="A77" t="s">
+        <v>122</v>
+      </c>
       <c r="B77" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>124</v>
+      </c>
+      <c r="D77" t="s">
+        <v>125</v>
+      </c>
+      <c r="E77" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="78">
 		</row>
     <row r="79">
       <c r="A79" t="s">
+        <v>127</v>
+      </c>
+      <c r="B79" t="s">
         <v>128</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79" t="s">
         <v>129</v>
       </c>
-      <c r="C79" t="s">
+      <c r="E79" t="s">
         <v>130</v>
-      </c>
-      <c r="D79" t="s">
-        <v>131</v>
-      </c>
-      <c r="E79" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="80">
 		</row>
     <row r="81">
       <c r="A81" t="s">
-        <v>133</v>
-      </c>
-      <c r="B81" t="s">
-        <v>129</v>
-      </c>
-      <c r="C81" t="s">
-        <v>130</v>
-      </c>
-      <c r="D81" t="s">
         <v>131</v>
       </c>
-      <c r="E81" t="s">
+    </row>
+    <row r="82">
+		</row>
+    <row r="83">
+      <c r="B83" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="82">
-		</row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>134</v>
-      </c>
-      <c r="B83" t="s">
-        <v>135</v>
-      </c>
-      <c r="D83" t="s">
-        <v>136</v>
-      </c>
-      <c r="E83" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="84">
-		</row>
     <row r="85">
-      <c r="A85" t="s">
-        <v>137</v>
-      </c>
       <c r="B85" t="s">
-        <v>135</v>
-      </c>
-      <c r="D85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="C85" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="s">
-        <v>36</v>
-      </c>
-      <c r="C86" t="s">
-        <v>36</v>
-      </c>
-    </row>
+		</row>
     <row r="87">
       <c r="A87" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
+        <v>134</v>
+      </c>
+      <c r="C87" t="s">
         <v>135</v>
       </c>
       <c r="D87" t="s">
         <v>136</v>
       </c>
       <c r="E87" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" t="s">
-        <v>38</v>
-      </c>
-    </row>
+		</row>
     <row r="89">
-		</row>
+      <c r="A89" t="s">
+        <v>138</v>
+      </c>
+      <c r="B89" t="s">
+        <v>139</v>
+      </c>
+      <c r="C89" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" t="s">
+        <v>141</v>
+      </c>
+      <c r="E89" t="s">
+        <v>142</v>
+      </c>
+    </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B90" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C90" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E90" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="91">
-		</row>
+      <c r="B91" t="s">
+        <v>35</v>
+      </c>
+      <c r="C91" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B92" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E92" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="s">
-        <v>149</v>
-      </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>37</v>
       </c>
       <c r="C93" t="s">
-        <v>151</v>
-      </c>
-      <c r="D93" t="s">
-        <v>152</v>
-      </c>
-      <c r="E93" t="s">
-        <v>153</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94" t="s">
-        <v>36</v>
-      </c>
-    </row>
+		</row>
     <row r="95">
       <c r="A95" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" t="s">
+        <v>150</v>
+      </c>
+      <c r="C95" t="s">
+        <v>151</v>
+      </c>
+      <c r="D95" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="96">
+		</row>
+    <row r="97">
+      <c r="A97" t="s">
         <v>154</v>
       </c>
-      <c r="B95" t="s">
-        <v>140</v>
-      </c>
-      <c r="C95" t="s">
-        <v>141</v>
-      </c>
-      <c r="D95" t="s">
-        <v>142</v>
-      </c>
-      <c r="E95" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" t="s">
-        <v>38</v>
-      </c>
-      <c r="C96" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="97">
-		</row>
+      <c r="B97" t="s">
+        <v>155</v>
+      </c>
+      <c r="C97" t="s">
+        <v>151</v>
+      </c>
+      <c r="D97" t="s">
+        <v>156</v>
+      </c>
+      <c r="E97" t="s">
+        <v>157</v>
+      </c>
+    </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B98" t="s">
-        <v>156</v>
-      </c>
-      <c r="C98" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D98" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E98" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
-		</row>
+      <c r="B99" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B100" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D100" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E100" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="s">
+      <c r="B101" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102">
+		</row>
+    <row r="103">
+      <c r="B103" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
         <v>163</v>
       </c>
-      <c r="B101" t="s">
-        <v>164</v>
-      </c>
-      <c r="D101" t="s">
-        <v>165</v>
-      </c>
-      <c r="E101" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" t="s">
-        <v>36</v>
-      </c>
-      <c r="C102" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>166</v>
-      </c>
-      <c r="B103" t="s">
-        <v>156</v>
-      </c>
-      <c r="C103" t="s">
-        <v>157</v>
-      </c>
-      <c r="D103" t="s">
-        <v>158</v>
-      </c>
-      <c r="E103" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="104">
       <c r="B104" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="C104" t="s">
-        <v>38</v>
+        <v>124</v>
+      </c>
+      <c r="D104" t="s">
+        <v>129</v>
+      </c>
+      <c r="E104" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="105">
-		</row>
+      <c r="B105" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="B106" t="s">
-        <v>36</v>
-      </c>
-      <c r="C106" t="s">
-        <v>36</v>
-      </c>
-    </row>
+		</row>
     <row r="107">
       <c r="A107" t="s">
+        <v>164</v>
+      </c>
+      <c r="B107" t="s">
+        <v>165</v>
+      </c>
+      <c r="D107" t="s">
+        <v>166</v>
+      </c>
+      <c r="E107" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="108">
+		</row>
+    <row r="109">
+      <c r="A109" t="s">
         <v>167</v>
       </c>
-      <c r="B107" t="s">
-        <v>129</v>
-      </c>
-      <c r="C107" t="s">
-        <v>130</v>
-      </c>
-      <c r="D107" t="s">
-        <v>131</v>
-      </c>
-      <c r="E107" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" t="s">
-        <v>38</v>
-      </c>
-      <c r="C108" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="109">
-		</row>
+      <c r="B109" t="s">
+        <v>165</v>
+      </c>
+      <c r="D109" t="s">
+        <v>166</v>
+      </c>
+      <c r="E109" t="s">
+        <v>161</v>
+      </c>
+    </row>
     <row r="110">
-      <c r="A110" t="s">
+		</row>
+    <row r="111">
+      <c r="A111" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="111">
-		</row>
+      <c r="B111" t="s">
+        <v>165</v>
+      </c>
+      <c r="D111" t="s">
+        <v>166</v>
+      </c>
+      <c r="E111" t="s">
+        <v>161</v>
+      </c>
+    </row>
     <row r="112">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="113">
-		</row>
+      <c r="B113" t="s">
+        <v>165</v>
+      </c>
+      <c r="D113" t="s">
+        <v>166</v>
+      </c>
+      <c r="E113" t="s">
+        <v>161</v>
+      </c>
+    </row>
     <row r="114">
       <c r="B114" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C114" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="B115" t="s">
+        <v>35</v>
+      </c>
+      <c r="C115" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="116">
       <c r="B116" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" t="s">
-        <v>38</v>
+        <v>165</v>
+      </c>
+      <c r="D116" t="s">
+        <v>166</v>
+      </c>
+      <c r="E116" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C117" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s">
+      <c r="B118" t="s">
+        <v>35</v>
+      </c>
+      <c r="C118" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="119">
       <c r="B119" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>38</v>
+        <v>124</v>
+      </c>
+      <c r="D119" t="s">
+        <v>125</v>
+      </c>
+      <c r="E119" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="s">
+        <v>172</v>
+      </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>173</v>
       </c>
       <c r="C120" t="s">
-        <v>36</v>
+        <v>174</v>
+      </c>
+      <c r="D120" t="s">
+        <v>175</v>
+      </c>
+      <c r="E120" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="s">
-        <v>172</v>
-      </c>
-      <c r="B121" t="s">
-        <v>129</v>
-      </c>
-      <c r="C121" t="s">
-        <v>130</v>
-      </c>
-      <c r="D121" t="s">
-        <v>131</v>
-      </c>
-      <c r="E121" t="s">
-        <v>132</v>
-      </c>
-    </row>
+		</row>
     <row r="122">
       <c r="A122" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B122" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C122" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D122" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E122" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="123">
 		</row>
     <row r="124">
       <c r="A124" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B124" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C124" t="s">
-        <v>180</v>
-      </c>
-      <c r="D124" t="s">
-        <v>181</v>
-      </c>
-      <c r="E124" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="125">
 		</row>
     <row r="126">
       <c r="A126" t="s">
+        <v>184</v>
+      </c>
+      <c r="B126" t="s">
         <v>183</v>
       </c>
-      <c r="B126" t="s">
-        <v>184</v>
-      </c>
       <c r="C126" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="127">
-		</row>
+      <c r="B127" t="s">
+        <v>35</v>
+      </c>
+      <c r="C127" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="128">
       <c r="A128" t="s">
         <v>185</v>
       </c>
       <c r="B128" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C128" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C129" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="s">
+		</row>
+    <row r="131">
+      <c r="A131" t="s">
         <v>186</v>
       </c>
-      <c r="B130" t="s">
-        <v>184</v>
-      </c>
-      <c r="C130" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="131">
       <c r="B131" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="C131" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
     </row>
     <row r="132">
 		</row>
     <row r="133">
       <c r="A133" t="s">
+        <v>188</v>
+      </c>
+      <c r="B133" t="s">
         <v>187</v>
       </c>
-      <c r="B133" t="s">
-        <v>188</v>
-      </c>
       <c r="C133" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="134">
-		</row>
+      <c r="B134" t="s">
+        <v>35</v>
+      </c>
+      <c r="C134" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="135">
       <c r="A135" t="s">
         <v>189</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C136" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
+		</row>
+    <row r="138">
+      <c r="A138" t="s">
         <v>190</v>
       </c>
-      <c r="B137" t="s">
-        <v>188</v>
-      </c>
-      <c r="C137" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="138">
       <c r="B138" t="s">
-        <v>38</v>
+        <v>191</v>
       </c>
       <c r="C138" t="s">
-        <v>38</v>
+        <v>192</v>
+      </c>
+      <c r="D138" t="s">
+        <v>180</v>
+      </c>
+      <c r="E138" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="139">
 		</row>
     <row r="140">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B140" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C140" t="s">
-        <v>193</v>
-      </c>
-      <c r="D140" t="s">
-        <v>181</v>
-      </c>
-      <c r="E140" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="141">
-		</row>
+      <c r="A141" t="s">
+        <v>196</v>
+      </c>
+      <c r="B141" t="s">
+        <v>197</v>
+      </c>
+      <c r="C141" t="s">
+        <v>198</v>
+      </c>
+      <c r="D141" t="s">
+        <v>180</v>
+      </c>
+      <c r="E141" t="s">
+        <v>199</v>
+      </c>
+    </row>
     <row r="142">
-      <c r="A142" t="s">
-        <v>195</v>
-      </c>
       <c r="B142" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C142" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B143" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C143" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D143" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E143" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C144" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
+      <c r="B145" t="s">
+        <v>35</v>
+      </c>
+      <c r="C145" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
         <v>201</v>
       </c>
-      <c r="B145" t="s">
-        <v>192</v>
-      </c>
-      <c r="C145" t="s">
-        <v>193</v>
-      </c>
-      <c r="D145" t="s">
+      <c r="B146" t="s">
+        <v>178</v>
+      </c>
+      <c r="C146" t="s">
+        <v>179</v>
+      </c>
+      <c r="D146" t="s">
+        <v>180</v>
+      </c>
+      <c r="E146" t="s">
         <v>181</v>
-      </c>
-      <c r="E145" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" t="s">
-        <v>38</v>
-      </c>
-      <c r="C146" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C147" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="148">
@@ -2918,99 +2924,74 @@
         <v>202</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="C148" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="D148" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="E148" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B150" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D150" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E150" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
-        <v>208</v>
-      </c>
       <c r="B152" t="s">
-        <v>174</v>
+        <v>6</v>
       </c>
       <c r="C152" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
       <c r="D152" t="s">
-        <v>176</v>
+        <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>177</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="C153" t="s">
-        <v>36</v>
+        <v>121</v>
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
-        <v>6</v>
-      </c>
-      <c r="C154" t="s">
-        <v>7</v>
-      </c>
-      <c r="D154" t="s">
-        <v>8</v>
-      </c>
-      <c r="E154" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" t="s">
-        <v>127</v>
-      </c>
-      <c r="C155" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="156">
 		</row>
   </sheetData>
 </worksheet>

--- a/SAP Reports/Input Files/Bal-Sht Feb 26/BS CHALLMC FEB 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/Bal-Sht Feb 26/BS CHALLMC FEB 26 ANNUAL.xlsx
@@ -14,81 +14,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="130">
   <si>
     <t>Account Name</t>
   </si>
   <si>
-    <t>Current Period</t>
-  </si>
-  <si>
-    <t>Comparison Period</t>
-  </si>
-  <si>
-    <t>Difference Amount</t>
-  </si>
-  <si>
-    <t>Percentage Difference</t>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>System Currency</t>
   </si>
   <si>
     <t>Assets</t>
   </si>
   <si>
-    <t>$  6,144,147.75</t>
-  </si>
-  <si>
-    <t>$  5,058,591.54</t>
-  </si>
-  <si>
-    <t>$ 1,085,556.21</t>
-  </si>
-  <si>
-    <t>% 21.460</t>
+    <t>$  6,095,536.38</t>
   </si>
   <si>
     <t>Current Assets - Cash and Equiv</t>
   </si>
   <si>
-    <t>$  6,001,294.01</t>
-  </si>
-  <si>
-    <t>$  4,930,027.59</t>
-  </si>
-  <si>
-    <t>$ 1,071,266.42</t>
-  </si>
-  <si>
-    <t>% 21.729</t>
+    <t>$  5,952,682.64</t>
   </si>
   <si>
     <t>Cash and Equiv - CASH AND EQUITY</t>
   </si>
   <si>
-    <t>$  4,374,595.12</t>
-  </si>
-  <si>
-    <t>$  2,146,549.01</t>
-  </si>
-  <si>
-    <t>$ 2,228,046.11</t>
-  </si>
-  <si>
-    <t>% 103.797</t>
+    <t>$  4,367,631.62</t>
   </si>
   <si>
     <t>110101-02-000-00 - SSB-CHECKING ACCT</t>
   </si>
   <si>
-    <t>$  783,024.30</t>
-  </si>
-  <si>
-    <t>$  1,439,593.84</t>
-  </si>
-  <si>
-    <t>$ -656,569.54</t>
-  </si>
-  <si>
-    <t>% -45.608</t>
+    <t>$  776,060.80</t>
   </si>
   <si>
     <t>110400-02-000-00 - SSB HIGH YIELD MMKT</t>
@@ -97,30 +55,12 @@
     <t>$  756,955.17</t>
   </si>
   <si>
-    <t>$  6,955.17</t>
-  </si>
-  <si>
-    <t>$ 750,000.00</t>
-  </si>
-  <si>
-    <t>% 10,783.345</t>
-  </si>
-  <si>
     <t>110450-02-000-00 - INTER DIVISION BANK</t>
   </si>
   <si>
     <t>$  2,834,615.65</t>
   </si>
   <si>
-    <t>$  700,000.00</t>
-  </si>
-  <si>
-    <t>$ 2,134,615.65</t>
-  </si>
-  <si>
-    <t>% 304.945</t>
-  </si>
-  <si>
     <t>__________________</t>
   </si>
   <si>
@@ -133,31 +73,13 @@
     <t>Receivables - RECEIVABLES</t>
   </si>
   <si>
-    <t>$  1,621,098.89</t>
-  </si>
-  <si>
-    <t>$  2,777,878.58</t>
-  </si>
-  <si>
-    <t>$ -1,156,779.69</t>
-  </si>
-  <si>
-    <t>% -41.643</t>
+    <t>$  1,579,451.02</t>
   </si>
   <si>
     <t>120000-02-000-00 - ACCOUNTS RECEIVABLE</t>
   </si>
   <si>
-    <t>$  3,551,831.35</t>
-  </si>
-  <si>
-    <t>$  3,809,611.04</t>
-  </si>
-  <si>
-    <t>$ -257,779.69</t>
-  </si>
-  <si>
-    <t>% -6.767</t>
+    <t>$  3,510,183.48</t>
   </si>
   <si>
     <t>120015-02-000-00 - LOAN TO/FROM TGI</t>
@@ -172,30 +94,12 @@
     <t>$ (2,100,000.00)</t>
   </si>
   <si>
-    <t>$ (1,200,000.00)</t>
-  </si>
-  <si>
-    <t>$ -900,000.00</t>
-  </si>
-  <si>
-    <t>% -75.000</t>
-  </si>
-  <si>
     <t>120060-02-000-00 - LOAN TO EMPLOYEE</t>
   </si>
   <si>
     <t>$  19,267.54</t>
   </si>
   <si>
-    <t>$  18,267.54</t>
-  </si>
-  <si>
-    <t>$ 1,000.00</t>
-  </si>
-  <si>
-    <t>% 5.474</t>
-  </si>
-  <si>
     <t>Total Receivables - RECEIVABLES</t>
   </si>
   <si>
@@ -220,27 +124,12 @@
     <t>$  20,002.74</t>
   </si>
   <si>
-    <t>$  5,712.95</t>
-  </si>
-  <si>
-    <t>$ 14,289.79</t>
-  </si>
-  <si>
-    <t>% 250.130</t>
-  </si>
-  <si>
     <t>FixedAssets - FIXED ASSETS</t>
   </si>
   <si>
     <t>$  1,735,786.09</t>
   </si>
   <si>
-    <t>$  1,721,496.30</t>
-  </si>
-  <si>
-    <t>% 0.830</t>
-  </si>
-  <si>
     <t>120470-02-000-00 - COMPUTER/OFFICE MACHINES</t>
   </si>
   <si>
@@ -265,30 +154,12 @@
     <t>$  691,993.64</t>
   </si>
   <si>
-    <t>$  686,703.85</t>
-  </si>
-  <si>
-    <t>$ 5,289.79</t>
-  </si>
-  <si>
-    <t>% 0.770</t>
-  </si>
-  <si>
     <t>120650-02-000-00 - HVAC</t>
   </si>
   <si>
     <t>$  208,256.56</t>
   </si>
   <si>
-    <t>$  199,256.56</t>
-  </si>
-  <si>
-    <t>$ 9,000.00</t>
-  </si>
-  <si>
-    <t>% 4.517</t>
-  </si>
-  <si>
     <t>120700-02-000-00 - VEHICLES &amp; HEAV EQUIP</t>
   </si>
   <si>
@@ -385,28 +256,13 @@
     <t>Liabilities</t>
   </si>
   <si>
-    <t>$  1,819,840.48</t>
-  </si>
-  <si>
-    <t>$  869,039.34</t>
-  </si>
-  <si>
-    <t>$ 950,801.14</t>
-  </si>
-  <si>
-    <t>% 109.408</t>
+    <t>$  1,818,172.25</t>
   </si>
   <si>
     <t>Current Liabs - CURRENT LIABILITIES</t>
   </si>
   <si>
-    <t>$  319,840.48</t>
-  </si>
-  <si>
-    <t>$ -549,198.86</t>
-  </si>
-  <si>
-    <t>% -63.196</t>
+    <t>$  318,172.25</t>
   </si>
   <si>
     <t>Accts Payable - ACCOUNTS PAYABLE</t>
@@ -418,46 +274,19 @@
     <t>Payroll Liabs - PAYROLL LIABILITIES</t>
   </si>
   <si>
-    <t>$  315,279.70</t>
-  </si>
-  <si>
-    <t>$  864,656.20</t>
-  </si>
-  <si>
-    <t>$ -549,376.50</t>
-  </si>
-  <si>
-    <t>% -63.537</t>
-  </si>
-  <si>
-    <t>220256-02-000-00 - WAGES PAYABLES</t>
+    <t>$  313,611.47</t>
+  </si>
+  <si>
+    <t>220256-02-000-00 - WAGES PAYABLE</t>
   </si>
   <si>
     <t>$  312,423.13</t>
   </si>
   <si>
-    <t>$  863,283.00</t>
-  </si>
-  <si>
-    <t>$ -550,859.87</t>
-  </si>
-  <si>
-    <t>% -63.810</t>
-  </si>
-  <si>
     <t>250900-02-000-00 - 401 K LIABILITY -PAYABLE</t>
   </si>
   <si>
-    <t>$  2,856.57</t>
-  </si>
-  <si>
-    <t>$  1,373.20</t>
-  </si>
-  <si>
-    <t>$ 1,483.37</t>
-  </si>
-  <si>
-    <t>% 108.023</t>
+    <t>$  1,188.34</t>
   </si>
   <si>
     <t>Total Payroll Liabs - PAYROLL LIABILITIES</t>
@@ -469,39 +298,18 @@
     <t>$  4,560.78</t>
   </si>
   <si>
-    <t>$  4,383.14</t>
-  </si>
-  <si>
-    <t>$ 177.64</t>
-  </si>
-  <si>
-    <t>% 4.053</t>
-  </si>
-  <si>
     <t>220260-02-000-00 - AFLAC PAYABLES</t>
   </si>
   <si>
     <t>$  4,307.76</t>
   </si>
   <si>
-    <t>$ -75.38</t>
-  </si>
-  <si>
-    <t>% -1.720</t>
-  </si>
-  <si>
     <t>250920-02-000-00 - HUMANA INS(VISION &amp; DENTAL)</t>
   </si>
   <si>
     <t>$  253.02</t>
   </si>
   <si>
-    <t>$ 253.02</t>
-  </si>
-  <si>
-    <t>****</t>
-  </si>
-  <si>
     <t>Total OtherLiability - OTHER LIBILITY</t>
   </si>
   <si>
@@ -514,9 +322,6 @@
     <t>$  1,500,000.00</t>
   </si>
   <si>
-    <t>$ 1,500,000.00</t>
-  </si>
-  <si>
     <t>Other L/T Liabs - OTHER LONG TERM LIBILITIES</t>
   </si>
   <si>
@@ -535,31 +340,13 @@
     <t>Equity</t>
   </si>
   <si>
-    <t>$  4,324,307.27</t>
-  </si>
-  <si>
-    <t>$  4,189,552.20</t>
-  </si>
-  <si>
-    <t>$ 134,755.07</t>
-  </si>
-  <si>
-    <t>% 3.216</t>
+    <t>$  4,277,364.13</t>
   </si>
   <si>
     <t>Stock Equity - STOCK HOLDERS EQUITY</t>
   </si>
   <si>
-    <t>$  3,676,458.56</t>
-  </si>
-  <si>
-    <t>$  3,595,458.56</t>
-  </si>
-  <si>
-    <t>$ 81,000.00</t>
-  </si>
-  <si>
-    <t>% 2.253</t>
+    <t>$  4,270,552.20</t>
   </si>
   <si>
     <t>Common Stock - COMMON STOCK</t>
@@ -589,19 +376,13 @@
     <t>Surplus - SURPLUS</t>
   </si>
   <si>
-    <t>$  3,257,245.56</t>
-  </si>
-  <si>
-    <t>$  3,176,245.56</t>
-  </si>
-  <si>
-    <t>% 2.550</t>
+    <t>$  3,851,339.20</t>
   </si>
   <si>
     <t>368400-02-000-00 - RETAINED EARNINGS</t>
   </si>
   <si>
-    <t>$  7,736,497.56</t>
+    <t>$  8,330,591.20</t>
   </si>
   <si>
     <t>368350-02-000-00 - PROFIT DISTRIBUTION</t>
@@ -610,12 +391,6 @@
     <t>$ (4,479,252.00)</t>
   </si>
   <si>
-    <t>$ (4,560,252.00)</t>
-  </si>
-  <si>
-    <t>% 1.776</t>
-  </si>
-  <si>
     <t>Total Surplus - SURPLUS</t>
   </si>
   <si>
@@ -625,16 +400,7 @@
     <t>Profit Period</t>
   </si>
   <si>
-    <t>$  647,848.71</t>
-  </si>
-  <si>
-    <t>$  594,093.64</t>
-  </si>
-  <si>
-    <t>$ 53,755.07</t>
-  </si>
-  <si>
-    <t>% 9.048</t>
+    <t>$  6,811.93</t>
   </si>
   <si>
     <t>Total Equity</t>
@@ -1495,1500 +1261,1230 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
 		</row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
 		</row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
 		</row>
     <row r="8">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
 		</row>
     <row r="15">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
 		</row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
 		</row>
     <row r="25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
 		</row>
     <row r="27">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
 		</row>
     <row r="32">
       <c r="B32" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
 		</row>
     <row r="36">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E36" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
 		</row>
     <row r="38">
       <c r="A38" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
 		</row>
     <row r="40">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" t="s">
-        <v>84</v>
-      </c>
-      <c r="E43" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D49" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" t="s">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
 		</row>
     <row r="52">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53">
 		</row>
     <row r="54">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C61" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C63" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
 		</row>
     <row r="66">
       <c r="B66" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
-        <v>68</v>
-      </c>
-      <c r="D67" t="s">
-        <v>69</v>
-      </c>
-      <c r="E67" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69">
 		</row>
     <row r="70">
       <c r="A70" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" t="s">
-        <v>8</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76">
 		</row>
     <row r="77">
       <c r="A77" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
-      </c>
-      <c r="D77" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78">
 		</row>
     <row r="79">
       <c r="A79" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
-      </c>
-      <c r="D79" t="s">
-        <v>129</v>
-      </c>
-      <c r="E79" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80">
 		</row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82">
 		</row>
     <row r="83">
       <c r="B83" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86">
 		</row>
     <row r="87">
       <c r="A87" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" t="s">
-        <v>136</v>
-      </c>
-      <c r="E87" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
 		</row>
     <row r="89">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>139</v>
+        <v>88</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
-      </c>
-      <c r="D89" t="s">
-        <v>141</v>
-      </c>
-      <c r="E89" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="C90" t="s">
-        <v>145</v>
-      </c>
-      <c r="D90" t="s">
-        <v>146</v>
-      </c>
-      <c r="E90" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="C92" t="s">
-        <v>135</v>
-      </c>
-      <c r="D92" t="s">
-        <v>136</v>
-      </c>
-      <c r="E92" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
 		</row>
     <row r="95">
       <c r="A95" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>151</v>
-      </c>
-      <c r="D95" t="s">
-        <v>152</v>
-      </c>
-      <c r="E95" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96">
 		</row>
     <row r="97">
       <c r="A97" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="B97" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>151</v>
-      </c>
-      <c r="D97" t="s">
-        <v>156</v>
-      </c>
-      <c r="E97" t="s">
-        <v>157</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
-      </c>
-      <c r="D98" t="s">
-        <v>160</v>
-      </c>
-      <c r="E98" t="s">
-        <v>161</v>
+        <v>97</v>
+      </c>
+      <c r="C98" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C99" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>151</v>
-      </c>
-      <c r="D100" t="s">
-        <v>152</v>
-      </c>
-      <c r="E100" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
 		</row>
     <row r="103">
       <c r="B103" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C103" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="B104" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
-      </c>
-      <c r="D104" t="s">
-        <v>129</v>
-      </c>
-      <c r="E104" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106">
 		</row>
     <row r="107">
       <c r="A107" t="s">
-        <v>164</v>
+        <v>100</v>
       </c>
       <c r="B107" t="s">
-        <v>165</v>
-      </c>
-      <c r="D107" t="s">
-        <v>166</v>
-      </c>
-      <c r="E107" t="s">
-        <v>161</v>
+        <v>101</v>
+      </c>
+      <c r="C107" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="108">
 		</row>
     <row r="109">
       <c r="A109" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="B109" t="s">
-        <v>165</v>
-      </c>
-      <c r="D109" t="s">
-        <v>166</v>
-      </c>
-      <c r="E109" t="s">
-        <v>161</v>
+        <v>101</v>
+      </c>
+      <c r="C109" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="110">
 		</row>
     <row r="111">
       <c r="A111" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>165</v>
-      </c>
-      <c r="D111" t="s">
-        <v>166</v>
-      </c>
-      <c r="E111" t="s">
-        <v>161</v>
+        <v>101</v>
+      </c>
+      <c r="C111" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C112" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
-        <v>165</v>
-      </c>
-      <c r="D113" t="s">
-        <v>166</v>
-      </c>
-      <c r="E113" t="s">
-        <v>161</v>
+        <v>101</v>
+      </c>
+      <c r="C113" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C115" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="B116" t="s">
-        <v>165</v>
-      </c>
-      <c r="D116" t="s">
-        <v>166</v>
-      </c>
-      <c r="E116" t="s">
-        <v>161</v>
+        <v>101</v>
+      </c>
+      <c r="C116" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="C119" t="s">
-        <v>124</v>
-      </c>
-      <c r="D119" t="s">
-        <v>125</v>
-      </c>
-      <c r="E119" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="B120" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="C120" t="s">
-        <v>174</v>
-      </c>
-      <c r="D120" t="s">
-        <v>175</v>
-      </c>
-      <c r="E120" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="121">
 		</row>
     <row r="122">
       <c r="A122" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="B122" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="C122" t="s">
-        <v>179</v>
-      </c>
-      <c r="D122" t="s">
-        <v>180</v>
-      </c>
-      <c r="E122" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123">
 		</row>
     <row r="124">
       <c r="A124" t="s">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="B124" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C124" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125">
 		</row>
     <row r="126">
       <c r="A126" t="s">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="B126" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C126" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="B128" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130">
 		</row>
     <row r="131">
       <c r="A131" t="s">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="B131" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="C131" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="132">
 		</row>
     <row r="133">
       <c r="A133" t="s">
-        <v>188</v>
+        <v>117</v>
       </c>
       <c r="B133" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="C133" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C134" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>189</v>
+        <v>118</v>
       </c>
       <c r="B135" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="C135" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C136" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137">
 		</row>
     <row r="138">
       <c r="A138" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="B138" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C138" t="s">
-        <v>192</v>
-      </c>
-      <c r="D138" t="s">
-        <v>180</v>
-      </c>
-      <c r="E138" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="139">
 		</row>
     <row r="140">
       <c r="A140" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="B140" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="C140" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>196</v>
+        <v>123</v>
       </c>
       <c r="B141" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="C141" t="s">
-        <v>198</v>
-      </c>
-      <c r="D141" t="s">
-        <v>180</v>
-      </c>
-      <c r="E141" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="B143" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="C143" t="s">
-        <v>192</v>
-      </c>
-      <c r="D143" t="s">
-        <v>180</v>
-      </c>
-      <c r="E143" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C144" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C145" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="B146" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="C146" t="s">
-        <v>179</v>
-      </c>
-      <c r="D146" t="s">
-        <v>180</v>
-      </c>
-      <c r="E146" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C147" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="B148" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="C148" t="s">
-        <v>204</v>
-      </c>
-      <c r="D148" t="s">
-        <v>205</v>
-      </c>
-      <c r="E148" t="s">
-        <v>206</v>
+        <v>128</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="B150" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="C150" t="s">
-        <v>174</v>
-      </c>
-      <c r="D150" t="s">
-        <v>175</v>
-      </c>
-      <c r="E150" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>7</v>
-      </c>
-      <c r="D152" t="s">
-        <v>8</v>
-      </c>
-      <c r="E152" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="C153" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
     </row>
     <row r="154">
